--- a/artfynd/A 38356-2021 artfynd.xlsx
+++ b/artfynd/A 38356-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134365431</v>
       </c>
       <c r="B2" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38356-2021 artfynd.xlsx
+++ b/artfynd/A 38356-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134365431</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
